--- a/artfynd/A 21800-2026 artfynd.xlsx
+++ b/artfynd/A 21800-2026 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
